--- a/27飞镖项目验收文档.xlsx
+++ b/27飞镖项目验收文档.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="26">
     <font>
       <name val="新細明體"/>
@@ -1606,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>46346</v>
+        <v>46341</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -1656,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>46380</v>
+        <v>46387</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -1706,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>46422</v>
+        <v>46399</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1756,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>46468</v>
+        <v>46447</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>

--- a/27飞镖项目验收文档.xlsx
+++ b/27飞镖项目验收文档.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+  </numFmts>
   <fonts count="26">
     <font>
       <name val="新細明體"/>
@@ -682,7 +684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,6 +708,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常規" xfId="0" builtinId="0"/>
@@ -1251,7 +1256,7 @@
       <c r="F4" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="9" t="n">
         <v>46325</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1259,7 +1264,7 @@
           <t>完成所有图纸和采购</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="9" t="n">
         <v>46330</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -1311,7 +1316,7 @@
           <t>完成新版机械镖图纸</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>46325</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1353,7 +1358,7 @@
       <c r="F6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="9" t="n">
         <v>46325</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1361,7 +1366,7 @@
           <t>完成一体化电池仓</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>46330</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1405,7 +1410,7 @@
       </c>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>46362</v>
       </c>
       <c r="J7" s="6" t="n"/>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>46034</v>
       </c>
       <c r="J8" s="6" t="n"/>
@@ -1485,7 +1490,7 @@
       </c>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="n"/>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="9" t="n">
         <v>46034</v>
       </c>
       <c r="J9" s="6" t="n"/>
@@ -1525,7 +1530,7 @@
       </c>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="9" t="n">
         <v>46081</v>
       </c>
       <c r="J10" s="6" t="n"/>
@@ -1565,7 +1570,7 @@
       </c>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="9" t="n">
         <v>46125</v>
       </c>
       <c r="J11" s="6" t="n"/>
@@ -1603,7 +1608,7 @@
       <c r="F12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="9" t="n">
         <v>46341</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1611,7 +1616,7 @@
           <t>跑通镖架瞄准与标定流程</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="9" t="n">
         <v>46362</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -1653,7 +1658,7 @@
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="9" t="n">
         <v>46387</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1661,7 +1666,7 @@
           <t>完成前哨站瞄准参数标定</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="9" t="n">
         <v>46399</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -1703,7 +1708,7 @@
       <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="9" t="n">
         <v>46399</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1711,7 +1716,7 @@
           <t>完成制导镖视觉跟踪与指令下发</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="9" t="n">
         <v>46446</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -1753,7 +1758,7 @@
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="9" t="n">
         <v>46447</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1761,7 +1766,7 @@
           <t>参数化标定与鲁棒性测试</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="9" t="n">
         <v>46490</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
